--- a/artfynd/A 14039-2026 artfynd.xlsx
+++ b/artfynd/A 14039-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131930257</v>
       </c>
       <c r="B2" t="n">
-        <v>58629</v>
+        <v>58631</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>131930272</v>
       </c>
       <c r="B3" t="n">
-        <v>58320</v>
+        <v>58322</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>131930249</v>
       </c>
       <c r="B4" t="n">
-        <v>101301</v>
+        <v>101304</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>132330928</v>
       </c>
       <c r="B5" t="n">
-        <v>92313</v>
+        <v>92316</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>132330847</v>
       </c>
       <c r="B7" t="n">
-        <v>58105</v>
+        <v>58107</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>132330750</v>
       </c>
       <c r="B8" t="n">
-        <v>91873</v>
+        <v>91876</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>131930240</v>
       </c>
       <c r="B10" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 14039-2026 artfynd.xlsx
+++ b/artfynd/A 14039-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131930257</v>
+        <v>131930272</v>
       </c>
       <c r="B2" t="n">
-        <v>58631</v>
+        <v>58322</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578897</v>
+        <v>578792</v>
       </c>
       <c r="R2" t="n">
-        <v>6432240</v>
+        <v>6432116</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131930272</v>
+        <v>131930257</v>
       </c>
       <c r="B3" t="n">
-        <v>58322</v>
+        <v>58631</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,16 +805,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578792</v>
+        <v>578897</v>
       </c>
       <c r="R3" t="n">
-        <v>6432116</v>
+        <v>6432240</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>

--- a/artfynd/A 14039-2026 artfynd.xlsx
+++ b/artfynd/A 14039-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131930272</v>
+        <v>131930257</v>
       </c>
       <c r="B2" t="n">
-        <v>58322</v>
+        <v>58632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578792</v>
+        <v>578897</v>
       </c>
       <c r="R2" t="n">
-        <v>6432116</v>
+        <v>6432240</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131930257</v>
+        <v>131930272</v>
       </c>
       <c r="B3" t="n">
-        <v>58631</v>
+        <v>58323</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,16 +805,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578897</v>
+        <v>578792</v>
       </c>
       <c r="R3" t="n">
-        <v>6432240</v>
+        <v>6432116</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -916,7 +916,7 @@
         <v>131930249</v>
       </c>
       <c r="B4" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>132330928</v>
       </c>
       <c r="B5" t="n">
-        <v>92316</v>
+        <v>92322</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>132330646</v>
       </c>
       <c r="B6" t="n">
-        <v>57961</v>
+        <v>57962</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>132330847</v>
       </c>
       <c r="B7" t="n">
-        <v>58107</v>
+        <v>58108</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>132330750</v>
       </c>
       <c r="B8" t="n">
-        <v>91876</v>
+        <v>91882</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>132330711</v>
       </c>
       <c r="B9" t="n">
-        <v>57869</v>
+        <v>57870</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>131930240</v>
       </c>
       <c r="B10" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 14039-2026 artfynd.xlsx
+++ b/artfynd/A 14039-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131930257</v>
+        <v>131930272</v>
       </c>
       <c r="B2" t="n">
-        <v>58632</v>
+        <v>58327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578897</v>
+        <v>578792</v>
       </c>
       <c r="R2" t="n">
-        <v>6432240</v>
+        <v>6432116</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131930272</v>
+        <v>131930257</v>
       </c>
       <c r="B3" t="n">
-        <v>58323</v>
+        <v>58636</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,16 +805,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578792</v>
+        <v>578897</v>
       </c>
       <c r="R3" t="n">
-        <v>6432116</v>
+        <v>6432240</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -916,7 +916,7 @@
         <v>131930249</v>
       </c>
       <c r="B4" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>132330928</v>
       </c>
       <c r="B5" t="n">
-        <v>92322</v>
+        <v>92332</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>132330646</v>
       </c>
       <c r="B6" t="n">
-        <v>57962</v>
+        <v>57966</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>132330847</v>
       </c>
       <c r="B7" t="n">
-        <v>58108</v>
+        <v>58112</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1362,45 +1362,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132330750</v>
+        <v>132330711</v>
       </c>
       <c r="B8" t="n">
-        <v>91882</v>
+        <v>57874</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4660</v>
+        <v>100001</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1411,7 +1408,7 @@
         <v>578882</v>
       </c>
       <c r="R8" t="n">
-        <v>6432221</v>
+        <v>6432217</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1448,16 +1445,15 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På klen asp</t>
+          <t>Plockat en ringduva</t>
         </is>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF8" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1476,42 +1472,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132330711</v>
+        <v>132330750</v>
       </c>
       <c r="B9" t="n">
-        <v>57870</v>
+        <v>91892</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100001</v>
+        <v>4660</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1522,7 +1521,7 @@
         <v>578882</v>
       </c>
       <c r="R9" t="n">
-        <v>6432217</v>
+        <v>6432221</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,15 +1558,16 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Plockat en ringduva</t>
+          <t>På klen asp</t>
         </is>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1589,7 +1589,7 @@
         <v>131930240</v>
       </c>
       <c r="B10" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 14039-2026 artfynd.xlsx
+++ b/artfynd/A 14039-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131930272</v>
+        <v>131930257</v>
       </c>
       <c r="B2" t="n">
-        <v>58327</v>
+        <v>58636</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578792</v>
+        <v>578897</v>
       </c>
       <c r="R2" t="n">
-        <v>6432116</v>
+        <v>6432240</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131930257</v>
+        <v>131930272</v>
       </c>
       <c r="B3" t="n">
-        <v>58636</v>
+        <v>58327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,16 +805,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578897</v>
+        <v>578792</v>
       </c>
       <c r="R3" t="n">
-        <v>6432240</v>
+        <v>6432116</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -1028,7 +1028,7 @@
         <v>132330928</v>
       </c>
       <c r="B5" t="n">
-        <v>92332</v>
+        <v>92333</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1362,42 +1362,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132330711</v>
+        <v>132330750</v>
       </c>
       <c r="B8" t="n">
-        <v>57874</v>
+        <v>91893</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100001</v>
+        <v>4660</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1408,7 +1411,7 @@
         <v>578882</v>
       </c>
       <c r="R8" t="n">
-        <v>6432217</v>
+        <v>6432221</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1445,15 +1448,16 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Plockat en ringduva</t>
+          <t>På klen asp</t>
         </is>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1472,45 +1476,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132330750</v>
+        <v>132330711</v>
       </c>
       <c r="B9" t="n">
-        <v>91892</v>
+        <v>57874</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4660</v>
+        <v>100001</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1521,7 +1522,7 @@
         <v>578882</v>
       </c>
       <c r="R9" t="n">
-        <v>6432221</v>
+        <v>6432217</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1558,16 +1559,15 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På klen asp</t>
+          <t>Plockat en ringduva</t>
         </is>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF9" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1589,7 +1589,7 @@
         <v>131930240</v>
       </c>
       <c r="B10" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 14039-2026 artfynd.xlsx
+++ b/artfynd/A 14039-2026 artfynd.xlsx
@@ -1362,45 +1362,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132330750</v>
+        <v>132330711</v>
       </c>
       <c r="B8" t="n">
-        <v>91893</v>
+        <v>57874</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4660</v>
+        <v>100001</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1411,7 +1408,7 @@
         <v>578882</v>
       </c>
       <c r="R8" t="n">
-        <v>6432221</v>
+        <v>6432217</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1448,16 +1445,15 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På klen asp</t>
+          <t>Plockat en ringduva</t>
         </is>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF8" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1476,42 +1472,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132330711</v>
+        <v>132330750</v>
       </c>
       <c r="B9" t="n">
-        <v>57874</v>
+        <v>91893</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100001</v>
+        <v>4660</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1522,7 +1521,7 @@
         <v>578882</v>
       </c>
       <c r="R9" t="n">
-        <v>6432217</v>
+        <v>6432221</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,15 +1558,16 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Plockat en ringduva</t>
+          <t>På klen asp</t>
         </is>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1589,7 +1589,7 @@
         <v>131930240</v>
       </c>
       <c r="B10" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 14039-2026 artfynd.xlsx
+++ b/artfynd/A 14039-2026 artfynd.xlsx
@@ -1362,42 +1362,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132330711</v>
+        <v>132330750</v>
       </c>
       <c r="B8" t="n">
-        <v>57874</v>
+        <v>91893</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100001</v>
+        <v>4660</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1408,7 +1411,7 @@
         <v>578882</v>
       </c>
       <c r="R8" t="n">
-        <v>6432217</v>
+        <v>6432221</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1445,15 +1448,16 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Plockat en ringduva</t>
+          <t>På klen asp</t>
         </is>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1472,45 +1476,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132330750</v>
+        <v>132330711</v>
       </c>
       <c r="B9" t="n">
-        <v>91893</v>
+        <v>57874</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4660</v>
+        <v>100001</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1521,7 +1522,7 @@
         <v>578882</v>
       </c>
       <c r="R9" t="n">
-        <v>6432221</v>
+        <v>6432217</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1558,16 +1559,15 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På klen asp</t>
+          <t>Plockat en ringduva</t>
         </is>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF9" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 14039-2026 artfynd.xlsx
+++ b/artfynd/A 14039-2026 artfynd.xlsx
@@ -1362,45 +1362,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132330750</v>
+        <v>132330711</v>
       </c>
       <c r="B8" t="n">
-        <v>91893</v>
+        <v>57874</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4660</v>
+        <v>100001</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1411,7 +1408,7 @@
         <v>578882</v>
       </c>
       <c r="R8" t="n">
-        <v>6432221</v>
+        <v>6432217</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1448,16 +1445,15 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På klen asp</t>
+          <t>Plockat en ringduva</t>
         </is>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF8" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1476,42 +1472,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132330711</v>
+        <v>132330750</v>
       </c>
       <c r="B9" t="n">
-        <v>57874</v>
+        <v>91893</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100001</v>
+        <v>4660</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1522,7 +1521,7 @@
         <v>578882</v>
       </c>
       <c r="R9" t="n">
-        <v>6432217</v>
+        <v>6432221</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,15 +1558,16 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Plockat en ringduva</t>
+          <t>På klen asp</t>
         </is>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 14039-2026 artfynd.xlsx
+++ b/artfynd/A 14039-2026 artfynd.xlsx
@@ -1028,7 +1028,7 @@
         <v>132330928</v>
       </c>
       <c r="B5" t="n">
-        <v>92333</v>
+        <v>92334</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>132330646</v>
       </c>
       <c r="B6" t="n">
-        <v>57966</v>
+        <v>57967</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>132330847</v>
       </c>
       <c r="B7" t="n">
-        <v>58112</v>
+        <v>58113</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1362,42 +1362,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132330711</v>
+        <v>132330750</v>
       </c>
       <c r="B8" t="n">
-        <v>57874</v>
+        <v>91894</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100001</v>
+        <v>4660</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1408,7 +1411,7 @@
         <v>578882</v>
       </c>
       <c r="R8" t="n">
-        <v>6432217</v>
+        <v>6432221</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1445,15 +1448,16 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Plockat en ringduva</t>
+          <t>På klen asp</t>
         </is>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1472,45 +1476,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132330750</v>
+        <v>132330711</v>
       </c>
       <c r="B9" t="n">
-        <v>91893</v>
+        <v>57875</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4660</v>
+        <v>100001</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1521,7 +1522,7 @@
         <v>578882</v>
       </c>
       <c r="R9" t="n">
-        <v>6432221</v>
+        <v>6432217</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1558,16 +1559,15 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På klen asp</t>
+          <t>Plockat en ringduva</t>
         </is>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF9" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1589,7 +1589,7 @@
         <v>131930240</v>
       </c>
       <c r="B10" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 14039-2026 artfynd.xlsx
+++ b/artfynd/A 14039-2026 artfynd.xlsx
@@ -1028,7 +1028,7 @@
         <v>132330928</v>
       </c>
       <c r="B5" t="n">
-        <v>92334</v>
+        <v>92336</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>132330750</v>
       </c>
       <c r="B8" t="n">
-        <v>91894</v>
+        <v>91896</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>131930240</v>
       </c>
       <c r="B10" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 14039-2026 artfynd.xlsx
+++ b/artfynd/A 14039-2026 artfynd.xlsx
@@ -1028,7 +1028,7 @@
         <v>132330928</v>
       </c>
       <c r="B5" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>132330750</v>
       </c>
       <c r="B8" t="n">
-        <v>91896</v>
+        <v>91897</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>131930240</v>
       </c>
       <c r="B10" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 14039-2026 artfynd.xlsx
+++ b/artfynd/A 14039-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131930257</v>
+        <v>132330928</v>
       </c>
       <c r="B2" t="n">
-        <v>58636</v>
+        <v>92370</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>4217</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -708,27 +708,26 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hyllsjön, Hyllela, Sm</t>
+          <t>A 14039, Hyllela, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578897</v>
+        <v>578852</v>
       </c>
       <c r="R2" t="n">
-        <v>6432240</v>
+        <v>6432117</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,22 +751,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:30</t>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På talllåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,28 +770,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ante Hultgren</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ante Hultgren</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131930272</v>
+        <v>132330750</v>
       </c>
       <c r="B3" t="n">
-        <v>58327</v>
+        <v>91958</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,21 +800,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>4660</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -827,27 +822,26 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hyllsjön, Hyllela, Sm</t>
+          <t>A 14039, Hyllela, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578792</v>
+        <v>578882</v>
       </c>
       <c r="R3" t="n">
-        <v>6432116</v>
+        <v>6432221</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,94 +865,94 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:30</t>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På klen asp</t>
         </is>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ante Hultgren</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ante Hultgren</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131930249</v>
+        <v>132330711</v>
       </c>
       <c r="B4" t="n">
-        <v>101323</v>
+        <v>57896</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>100001</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hyllsjön, Hyllela, Sm</t>
+          <t>A 14039, Hyllela, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578831</v>
+        <v>578882</v>
       </c>
       <c r="R4" t="n">
-        <v>6432134</v>
+        <v>6432217</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,22 +976,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Plockat en ringduva</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,64 +995,60 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ante Hultgren</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ante Hultgren</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132330928</v>
+        <v>132330794</v>
       </c>
       <c r="B5" t="n">
-        <v>92340</v>
+        <v>57896</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4217</v>
+        <v>100001</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1071,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578852</v>
+        <v>578710</v>
       </c>
       <c r="R5" t="n">
-        <v>6432117</v>
+        <v>6432133</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,7 +1096,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På talllåga</t>
+          <t>Plockat en ringduva</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,7 +1105,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1139,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132330646</v>
+        <v>132330900</v>
       </c>
       <c r="B6" t="n">
-        <v>57970</v>
+        <v>57896</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1150,16 +1134,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100048</v>
+        <v>100001</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1167,16 +1151,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1186,13 +1166,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578902</v>
+        <v>578708</v>
       </c>
       <c r="R6" t="n">
-        <v>6432249</v>
+        <v>6432141</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1226,7 +1206,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Trummade i strandskogen. Flög sedan troligen över sjön, där den hördes trumma.</t>
+          <t>Plockat en ringduva</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,10 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132330847</v>
+        <v>132330646</v>
       </c>
       <c r="B7" t="n">
-        <v>58116</v>
+        <v>57988</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1264,16 +1244,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103020</v>
+        <v>100048</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1336,6 +1316,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Trummade i strandskogen. Flög sedan troligen över sjön, där den hördes trumma.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,27 +1347,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132330711</v>
+        <v>131930272</v>
       </c>
       <c r="B8" t="n">
-        <v>57878</v>
+        <v>58349</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100001</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1390,28 +1375,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 14039, Hyllela, Sm</t>
+          <t>Hyllsjön, Hyllela, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>578882</v>
+        <v>578792</v>
       </c>
       <c r="R8" t="n">
-        <v>6432217</v>
+        <v>6432116</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1435,17 +1424,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Plockat en ringduva</t>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1460,44 +1454,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Ante Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Ante Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132330750</v>
+        <v>132330847</v>
       </c>
       <c r="B9" t="n">
-        <v>91900</v>
+        <v>58134</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4660</v>
+        <v>103020</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1505,12 +1499,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1518,13 +1513,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>578882</v>
+        <v>578902</v>
       </c>
       <c r="R9" t="n">
-        <v>6432221</v>
+        <v>6432249</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1556,18 +1551,12 @@
           <t>2026-04-10</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På klen asp</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF9" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1586,57 +1575,57 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131930240</v>
+        <v>131930257</v>
       </c>
       <c r="B10" t="n">
-        <v>99125</v>
+        <v>58658</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hyllsjön, Hyllela, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578887</v>
+        <v>578897</v>
       </c>
       <c r="R10" t="n">
-        <v>6432210</v>
+        <v>6432240</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1668,7 +1657,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1678,7 +1667,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1687,7 +1676,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1703,6 +1691,238 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>131930240</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hyllsjön, Hyllela, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>578887</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6432210</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Överum</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Ante Hultgren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Ante Hultgren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>131930249</v>
+      </c>
+      <c r="B12" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hyllsjön, Hyllela, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>578831</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6432134</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Överum</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Ante Hultgren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Ante Hultgren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
